--- a/df_log_20260306.xlsx
+++ b/df_log_20260306.xlsx
@@ -456,28 +456,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>부산시설관리공단</t>
+          <t>서울시설관리공단</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -489,25 +489,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>부산시설관리공단</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
